--- a/isms-core-framework/A.5-organizational-controls/isms-a.5.24-28-incident-management-lifecycle/WKBK/90_workbooks/ISMS-IMP-A.5.24-28.S4_Forensic_Evidence_20260208.xlsx
+++ b/isms-core-framework/A.5-organizational-controls/isms-a.5.24-28-incident-management-lifecycle/WKBK/90_workbooks/ISMS-IMP-A.5.24-28.S4_Forensic_Evidence_20260208.xlsx
@@ -3695,7 +3695,7 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>PCI DSS forensic evidence compliance?</t>
+          <t>PCI DSS v4.0.1 forensic evidence compliance?</t>
         </is>
       </c>
       <c r="D16" s="5" t="n"/>
